--- a/artfynd/A 45510-2023 artfynd.xlsx
+++ b/artfynd/A 45510-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45510-2023 artfynd.xlsx
+++ b/artfynd/A 45510-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106779691</v>
       </c>
       <c r="B2" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409896.870103524</v>
+        <v>409897</v>
       </c>
       <c r="R2" t="n">
-        <v>6300965.905564395</v>
+        <v>6300966</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,19 +759,9 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106779703</v>
+        <v>106779710</v>
       </c>
       <c r="B3" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -865,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409874.3961438223</v>
+        <v>409874</v>
       </c>
       <c r="R3" t="n">
-        <v>6300889.80002581</v>
+        <v>6300890</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -898,24 +878,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På en levande ek. Blandskog.</t>
+          <t>På en levande ek.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106779710</v>
+        <v>106779703</v>
       </c>
       <c r="B4" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,26 +924,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -999,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409874.3961438223</v>
+        <v>409874</v>
       </c>
       <c r="R4" t="n">
-        <v>6300889.80002581</v>
+        <v>6300890</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1032,24 +997,14 @@
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-14</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en levande ek.</t>
+          <t>På en levande ek. Blandskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 45510-2023 artfynd.xlsx
+++ b/artfynd/A 45510-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779691</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779710</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,8 +1044,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106779703</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>